--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$4</f>
+              <f>'Counts'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$4</f>
+              <f>'Counts'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$4</f>
+              <f>'Counts'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$4</f>
+              <f>'Counts'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -649,6 +649,19 @@
         <v>77</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>225</v>
+      </c>
+      <c r="C5" t="n">
+        <v>90</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -656,10 +656,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C5" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$5</f>
+              <f>'Counts'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$5</f>
+              <f>'Counts'!$B$2:$B$6</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$5</f>
+              <f>'Counts'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$5</f>
+              <f>'Counts'!$C$2:$C$6</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -660,6 +660,19 @@
       </c>
       <c r="C5" t="n">
         <v>89</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>223</v>
+      </c>
+      <c r="C6" t="n">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -669,10 +669,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="C6" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$6</f>
+              <f>'Counts'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$6</f>
+              <f>'Counts'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$6</f>
+              <f>'Counts'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$6</f>
+              <f>'Counts'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -673,6 +673,19 @@
       </c>
       <c r="C6" t="n">
         <v>79</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>231</v>
+      </c>
+      <c r="C7" t="n">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -682,10 +682,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C7" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$7</f>
+              <f>'Counts'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$7</f>
+              <f>'Counts'!$B$2:$B$8</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$7</f>
+              <f>'Counts'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$7</f>
+              <f>'Counts'!$C$2:$C$8</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -686,6 +686,19 @@
       </c>
       <c r="C7" t="n">
         <v>78</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>240</v>
+      </c>
+      <c r="C8" t="n">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="C8" t="n">
         <v>79</v>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$8</f>
+              <f>'Counts'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$8</f>
+              <f>'Counts'!$B$2:$B$9</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$8</f>
+              <f>'Counts'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$8</f>
+              <f>'Counts'!$C$2:$C$9</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -699,6 +699,19 @@
       </c>
       <c r="C8" t="n">
         <v>79</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>253</v>
+      </c>
+      <c r="C9" t="n">
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="C9" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$9</f>
+              <f>'Counts'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$9</f>
+              <f>'Counts'!$B$2:$B$10</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$9</f>
+              <f>'Counts'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$9</f>
+              <f>'Counts'!$C$2:$C$10</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -712,6 +712,19 @@
       </c>
       <c r="C9" t="n">
         <v>78</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>251</v>
+      </c>
+      <c r="C10" t="n">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="C10" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$10</f>
+              <f>'Counts'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$10</f>
+              <f>'Counts'!$B$2:$B$11</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$10</f>
+              <f>'Counts'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$10</f>
+              <f>'Counts'!$C$2:$C$11</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -725,6 +725,19 @@
       </c>
       <c r="C10" t="n">
         <v>80</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>250</v>
+      </c>
+      <c r="C11" t="n">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C11" t="n">
         <v>77</v>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$11</f>
+              <f>'Counts'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$11</f>
+              <f>'Counts'!$B$2:$B$12</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$11</f>
+              <f>'Counts'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$11</f>
+              <f>'Counts'!$C$2:$C$12</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -738,6 +738,19 @@
       </c>
       <c r="C11" t="n">
         <v>77</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>245</v>
+      </c>
+      <c r="C12" t="n">
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$12</f>
+              <f>'Counts'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$12</f>
+              <f>'Counts'!$B$2:$B$13</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$12</f>
+              <f>'Counts'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$12</f>
+              <f>'Counts'!$C$2:$C$13</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -751,6 +751,19 @@
       </c>
       <c r="C12" t="n">
         <v>72</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>238</v>
+      </c>
+      <c r="C13" t="n">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="C13" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -763,7 +763,7 @@
         <v>248</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$13</f>
+              <f>'Counts'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$13</f>
+              <f>'Counts'!$B$2:$B$14</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$13</f>
+              <f>'Counts'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$13</f>
+              <f>'Counts'!$C$2:$C$14</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,6 +763,19 @@
         <v>248</v>
       </c>
       <c r="C13" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>243</v>
+      </c>
+      <c r="C14" t="n">
         <v>119</v>
       </c>
     </row>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -773,10 +773,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C14" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -762,9 +762,6 @@
       <c r="B13" t="n">
         <v>248</v>
       </c>
-      <c r="C13" t="n">
-        <v>119</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -776,7 +773,7 @@
         <v>255</v>
       </c>
       <c r="C14" t="n">
-        <v>122</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -762,6 +762,9 @@
       <c r="B13" t="n">
         <v>248</v>
       </c>
+      <c r="C13" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$14</f>
+              <f>'Counts'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$14</f>
+              <f>'Counts'!$B$2:$B$15</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$14</f>
+              <f>'Counts'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$14</f>
+              <f>'Counts'!$C$2:$C$15</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -777,6 +777,19 @@
       </c>
       <c r="C14" t="n">
         <v>79</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>258</v>
+      </c>
+      <c r="C15" t="n">
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -786,10 +786,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$15</f>
+              <f>'Counts'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$15</f>
+              <f>'Counts'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$15</f>
+              <f>'Counts'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$15</f>
+              <f>'Counts'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,6 +790,19 @@
       </c>
       <c r="C15" t="n">
         <v>79</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>259</v>
+      </c>
+      <c r="C16" t="n">
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -799,10 +799,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C16" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$16</f>
+              <f>'Counts'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$16</f>
+              <f>'Counts'!$B$2:$B$17</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$16</f>
+              <f>'Counts'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$16</f>
+              <f>'Counts'!$C$2:$C$17</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,6 +803,19 @@
       </c>
       <c r="C16" t="n">
         <v>89</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>261</v>
+      </c>
+      <c r="C17" t="n">
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$17</f>
+              <f>'Counts'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$17</f>
+              <f>'Counts'!$B$2:$B$18</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$17</f>
+              <f>'Counts'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$17</f>
+              <f>'Counts'!$C$2:$C$18</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -816,6 +816,19 @@
       </c>
       <c r="C17" t="n">
         <v>74</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>261</v>
+      </c>
+      <c r="C18" t="n">
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$18</f>
+              <f>'Counts'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$18</f>
+              <f>'Counts'!$B$2:$B$19</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$18</f>
+              <f>'Counts'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$18</f>
+              <f>'Counts'!$C$2:$C$19</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -829,6 +829,19 @@
       </c>
       <c r="C18" t="n">
         <v>72</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>256</v>
+      </c>
+      <c r="C19" t="n">
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -841,7 +841,7 @@
         <v>256</v>
       </c>
       <c r="C19" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$19</f>
+              <f>'Counts'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$19</f>
+              <f>'Counts'!$B$2:$B$20</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$19</f>
+              <f>'Counts'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$19</f>
+              <f>'Counts'!$C$2:$C$20</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -842,6 +842,19 @@
       </c>
       <c r="C19" t="n">
         <v>66</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>249</v>
+      </c>
+      <c r="C20" t="n">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -854,7 +854,7 @@
         <v>249</v>
       </c>
       <c r="C20" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$20</f>
+              <f>'Counts'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$20</f>
+              <f>'Counts'!$B$2:$B$21</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$20</f>
+              <f>'Counts'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$20</f>
+              <f>'Counts'!$C$2:$C$21</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -855,6 +855,19 @@
       </c>
       <c r="C20" t="n">
         <v>64</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>245</v>
+      </c>
+      <c r="C21" t="n">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -864,10 +864,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C21" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$21</f>
+              <f>'Counts'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$21</f>
+              <f>'Counts'!$B$2:$B$22</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$21</f>
+              <f>'Counts'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$21</f>
+              <f>'Counts'!$C$2:$C$22</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -867,6 +867,19 @@
         <v>251</v>
       </c>
       <c r="C21" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>253</v>
+      </c>
+      <c r="C22" t="n">
         <v>66</v>
       </c>
     </row>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -877,10 +877,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C22" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$22</f>
+              <f>'Counts'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$22</f>
+              <f>'Counts'!$B$2:$B$23</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$22</f>
+              <f>'Counts'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$22</f>
+              <f>'Counts'!$C$2:$C$23</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -881,6 +881,19 @@
       </c>
       <c r="C22" t="n">
         <v>68</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>243</v>
+      </c>
+      <c r="C23" t="n">
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="C23" t="n">
         <v>66</v>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$23</f>
+              <f>'Counts'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$23</f>
+              <f>'Counts'!$B$2:$B$24</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$23</f>
+              <f>'Counts'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$23</f>
+              <f>'Counts'!$C$2:$C$24</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -894,6 +894,19 @@
       </c>
       <c r="C23" t="n">
         <v>66</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>237</v>
+      </c>
+      <c r="C24" t="n">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C24" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$24</f>
+              <f>'Counts'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$24</f>
+              <f>'Counts'!$B$2:$B$26</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$24</f>
+              <f>'Counts'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$24</f>
+              <f>'Counts'!$C$2:$C$26</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,6 +907,32 @@
       </c>
       <c r="C24" t="n">
         <v>68</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>234</v>
+      </c>
+      <c r="C25" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>226</v>
+      </c>
+      <c r="C26" t="n">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$26</f>
+              <f>'Counts'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$26</f>
+              <f>'Counts'!$B$2:$B$27</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$26</f>
+              <f>'Counts'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$26</f>
+              <f>'Counts'!$C$2:$C$27</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -933,6 +933,19 @@
       </c>
       <c r="C26" t="n">
         <v>61</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>218</v>
+      </c>
+      <c r="C27" t="n">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="C27" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$27</f>
+              <f>'Counts'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$27</f>
+              <f>'Counts'!$B$2:$B$28</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$27</f>
+              <f>'Counts'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$27</f>
+              <f>'Counts'!$C$2:$C$28</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -945,6 +945,19 @@
         <v>235</v>
       </c>
       <c r="C27" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>232</v>
+      </c>
+      <c r="C28" t="n">
         <v>62</v>
       </c>
     </row>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="C28" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$28</f>
+              <f>'Counts'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$28</f>
+              <f>'Counts'!$B$2:$B$29</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$28</f>
+              <f>'Counts'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$28</f>
+              <f>'Counts'!$C$2:$C$29</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -959,6 +959,19 @@
       </c>
       <c r="C28" t="n">
         <v>65</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>245</v>
+      </c>
+      <c r="C29" t="n">
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$29</f>
+              <f>'Counts'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$29</f>
+              <f>'Counts'!$B$2:$B$30</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$29</f>
+              <f>'Counts'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$29</f>
+              <f>'Counts'!$C$2:$C$30</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -972,6 +972,19 @@
       </c>
       <c r="C29" t="n">
         <v>64</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>244</v>
+      </c>
+      <c r="C30" t="n">
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="C30" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$30</f>
+              <f>'Counts'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$30</f>
+              <f>'Counts'!$B$2:$B$31</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$30</f>
+              <f>'Counts'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$30</f>
+              <f>'Counts'!$C$2:$C$31</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -985,6 +985,19 @@
       </c>
       <c r="C30" t="n">
         <v>73</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>240</v>
+      </c>
+      <c r="C31" t="n">
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C31" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$31</f>
+              <f>'Counts'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$31</f>
+              <f>'Counts'!$B$2:$B$32</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$31</f>
+              <f>'Counts'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$31</f>
+              <f>'Counts'!$C$2:$C$32</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -998,6 +998,19 @@
       </c>
       <c r="C31" t="n">
         <v>69</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>245</v>
+      </c>
+      <c r="C32" t="n">
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$32</f>
+              <f>'Counts'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$32</f>
+              <f>'Counts'!$B$2:$B$33</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$32</f>
+              <f>'Counts'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$32</f>
+              <f>'Counts'!$C$2:$C$33</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1011,6 +1011,19 @@
       </c>
       <c r="C32" t="n">
         <v>67</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>241</v>
+      </c>
+      <c r="C33" t="n">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C33" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$33</f>
+              <f>'Counts'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$33</f>
+              <f>'Counts'!$B$2:$B$34</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$33</f>
+              <f>'Counts'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$33</f>
+              <f>'Counts'!$C$2:$C$34</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1023,6 +1023,19 @@
         <v>243</v>
       </c>
       <c r="C33" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>233</v>
+      </c>
+      <c r="C34" t="n">
         <v>67</v>
       </c>
     </row>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C34" t="n">
         <v>67</v>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$34</f>
+              <f>'Counts'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$34</f>
+              <f>'Counts'!$B$2:$B$35</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$34</f>
+              <f>'Counts'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$34</f>
+              <f>'Counts'!$C$2:$C$35</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1037,6 +1037,19 @@
       </c>
       <c r="C34" t="n">
         <v>67</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>240</v>
+      </c>
+      <c r="C35" t="n">
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="C35" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$35</f>
+              <f>'Counts'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$35</f>
+              <f>'Counts'!$B$2:$B$36</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$35</f>
+              <f>'Counts'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$35</f>
+              <f>'Counts'!$C$2:$C$36</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1050,6 +1050,19 @@
       </c>
       <c r="C35" t="n">
         <v>67</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>248</v>
+      </c>
+      <c r="C36" t="n">
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C36" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$36</f>
+              <f>'Counts'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$36</f>
+              <f>'Counts'!$B$2:$B$37</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$36</f>
+              <f>'Counts'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$36</f>
+              <f>'Counts'!$C$2:$C$37</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,6 +1063,19 @@
       </c>
       <c r="C36" t="n">
         <v>67</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>243</v>
+      </c>
+      <c r="C37" t="n">
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="C37" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$37</f>
+              <f>'Counts'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$37</f>
+              <f>'Counts'!$B$2:$B$38</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$37</f>
+              <f>'Counts'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$37</f>
+              <f>'Counts'!$C$2:$C$38</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1076,6 +1076,16 @@
       </c>
       <c r="C37" t="n">
         <v>66</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -1087,6 +1087,9 @@
       <c r="B38" t="n">
         <v>238</v>
       </c>
+      <c r="C38" t="n">
+        <v>66</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C38" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$38</f>
+              <f>'Counts'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$38</f>
+              <f>'Counts'!$B$2:$B$39</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$38</f>
+              <f>'Counts'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$38</f>
+              <f>'Counts'!$C$2:$C$39</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1089,6 +1089,19 @@
       </c>
       <c r="C38" t="n">
         <v>68</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>231</v>
+      </c>
+      <c r="C39" t="n">
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$39</f>
+              <f>'Counts'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$39</f>
+              <f>'Counts'!$B$2:$B$40</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$39</f>
+              <f>'Counts'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$39</f>
+              <f>'Counts'!$C$2:$C$40</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1102,6 +1102,19 @@
       </c>
       <c r="C39" t="n">
         <v>66</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>223</v>
+      </c>
+      <c r="C40" t="n">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$40</f>
+              <f>'Counts'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$40</f>
+              <f>'Counts'!$B$2:$B$41</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$40</f>
+              <f>'Counts'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$40</f>
+              <f>'Counts'!$C$2:$C$41</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1115,6 +1115,19 @@
       </c>
       <c r="C40" t="n">
         <v>62</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>219</v>
+      </c>
+      <c r="C41" t="n">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C41" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$41</f>
+              <f>'Counts'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$41</f>
+              <f>'Counts'!$B$2:$B$42</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$41</f>
+              <f>'Counts'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$41</f>
+              <f>'Counts'!$C$2:$C$42</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1128,6 +1128,19 @@
       </c>
       <c r="C41" t="n">
         <v>63</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>216</v>
+      </c>
+      <c r="C42" t="n">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C42" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$42</f>
+              <f>'Counts'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$42</f>
+              <f>'Counts'!$B$2:$B$43</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$42</f>
+              <f>'Counts'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$42</f>
+              <f>'Counts'!$C$2:$C$43</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1141,6 +1141,19 @@
       </c>
       <c r="C42" t="n">
         <v>61</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>223</v>
+      </c>
+      <c r="C43" t="n">
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C43" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$43</f>
+              <f>'Counts'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$43</f>
+              <f>'Counts'!$B$2:$B$44</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$43</f>
+              <f>'Counts'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$43</f>
+              <f>'Counts'!$C$2:$C$44</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1154,6 +1154,19 @@
       </c>
       <c r="C43" t="n">
         <v>62</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>217</v>
+      </c>
+      <c r="C44" t="n">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="C44" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$44</f>
+              <f>'Counts'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$44</f>
+              <f>'Counts'!$B$2:$B$45</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$44</f>
+              <f>'Counts'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$44</f>
+              <f>'Counts'!$C$2:$C$45</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1167,6 +1167,19 @@
       </c>
       <c r="C44" t="n">
         <v>59</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>218</v>
+      </c>
+      <c r="C45" t="n">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="C45" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$45</f>
+              <f>'Counts'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$45</f>
+              <f>'Counts'!$B$2:$B$46</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$45</f>
+              <f>'Counts'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$45</f>
+              <f>'Counts'!$C$2:$C$46</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1179,6 +1179,19 @@
         <v>233</v>
       </c>
       <c r="C45" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>224</v>
+      </c>
+      <c r="C46" t="n">
         <v>56</v>
       </c>
     </row>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$46</f>
+              <f>'Counts'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$46</f>
+              <f>'Counts'!$B$2:$B$47</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$46</f>
+              <f>'Counts'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$46</f>
+              <f>'Counts'!$C$2:$C$47</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1193,6 +1193,19 @@
       </c>
       <c r="C46" t="n">
         <v>56</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>222</v>
+      </c>
+      <c r="C47" t="n">
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -1202,10 +1202,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C47" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$47</f>
+              <f>'Counts'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$47</f>
+              <f>'Counts'!$B$2:$B$48</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$47</f>
+              <f>'Counts'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$47</f>
+              <f>'Counts'!$C$2:$C$48</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1206,6 +1206,19 @@
       </c>
       <c r="C47" t="n">
         <v>56</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>217</v>
+      </c>
+      <c r="C48" t="n">
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="C48" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$48</f>
+              <f>'Counts'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$48</f>
+              <f>'Counts'!$B$2:$B$49</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$48</f>
+              <f>'Counts'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$48</f>
+              <f>'Counts'!$C$2:$C$49</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1219,6 +1219,19 @@
       </c>
       <c r="C48" t="n">
         <v>54</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>235</v>
+      </c>
+      <c r="C49" t="n">
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C49" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$49</f>
+              <f>'Counts'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$49</f>
+              <f>'Counts'!$B$2:$B$50</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$49</f>
+              <f>'Counts'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$49</f>
+              <f>'Counts'!$C$2:$C$50</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1232,6 +1232,19 @@
       </c>
       <c r="C49" t="n">
         <v>58</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>240</v>
+      </c>
+      <c r="C50" t="n">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C50" t="n">
         <v>75</v>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$50</f>
+              <f>'Counts'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$50</f>
+              <f>'Counts'!$B$2:$B$51</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$50</f>
+              <f>'Counts'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$50</f>
+              <f>'Counts'!$C$2:$C$51</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1244,6 +1244,19 @@
         <v>248</v>
       </c>
       <c r="C50" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>246</v>
+      </c>
+      <c r="C51" t="n">
         <v>75</v>
       </c>
     </row>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C51" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$51</f>
+              <f>'Counts'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$51</f>
+              <f>'Counts'!$B$2:$B$52</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$51</f>
+              <f>'Counts'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$51</f>
+              <f>'Counts'!$C$2:$C$52</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1258,6 +1258,19 @@
       </c>
       <c r="C51" t="n">
         <v>62</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>249</v>
+      </c>
+      <c r="C52" t="n">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C52" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$52</f>
+              <f>'Counts'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$52</f>
+              <f>'Counts'!$B$2:$B$53</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$52</f>
+              <f>'Counts'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$52</f>
+              <f>'Counts'!$C$2:$C$53</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1271,6 +1271,19 @@
       </c>
       <c r="C52" t="n">
         <v>59</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>243</v>
+      </c>
+      <c r="C53" t="n">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C53" t="n">
         <v>58</v>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$53</f>
+              <f>'Counts'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$53</f>
+              <f>'Counts'!$B$2:$B$54</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$53</f>
+              <f>'Counts'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$53</f>
+              <f>'Counts'!$C$2:$C$54</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1284,6 +1284,19 @@
       </c>
       <c r="C53" t="n">
         <v>58</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>244</v>
+      </c>
+      <c r="C54" t="n">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C54" t="n">
         <v>56</v>
